--- a/artfynd/A 24496-2025 artfynd.xlsx
+++ b/artfynd/A 24496-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130190567</v>
       </c>
       <c r="B3" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24496-2025 artfynd.xlsx
+++ b/artfynd/A 24496-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130190573</v>
       </c>
       <c r="B2" t="n">
-        <v>82939</v>
+        <v>83024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130190567</v>
       </c>
       <c r="B3" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130190556</v>
       </c>
       <c r="B4" t="n">
-        <v>57754</v>
+        <v>57839</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130190570</v>
       </c>
       <c r="B5" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>130190569</v>
       </c>
       <c r="B6" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24496-2025 artfynd.xlsx
+++ b/artfynd/A 24496-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130190573</v>
       </c>
       <c r="B2" t="n">
-        <v>83024</v>
+        <v>83027</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130190567</v>
       </c>
       <c r="B3" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,27 +899,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130190556</v>
+        <v>130190570</v>
       </c>
       <c r="B4" t="n">
-        <v>57839</v>
+        <v>58198</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>761916</v>
+        <v>761900</v>
       </c>
       <c r="R4" t="n">
-        <v>7181670</v>
+        <v>7181685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1011,27 +1011,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130190570</v>
+        <v>130190556</v>
       </c>
       <c r="B5" t="n">
-        <v>58198</v>
+        <v>57839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>761900</v>
+        <v>761916</v>
       </c>
       <c r="R5" t="n">
-        <v>7181685</v>
+        <v>7181670</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 24496-2025 artfynd.xlsx
+++ b/artfynd/A 24496-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130190573</v>
       </c>
       <c r="B2" t="n">
-        <v>83027</v>
+        <v>83053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130190567</v>
       </c>
       <c r="B3" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,27 +899,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130190570</v>
+        <v>130190556</v>
       </c>
       <c r="B4" t="n">
-        <v>58198</v>
+        <v>57865</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>761900</v>
+        <v>761916</v>
       </c>
       <c r="R4" t="n">
-        <v>7181685</v>
+        <v>7181670</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1011,27 +1011,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130190556</v>
+        <v>130190570</v>
       </c>
       <c r="B5" t="n">
-        <v>57839</v>
+        <v>58224</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>761916</v>
+        <v>761900</v>
       </c>
       <c r="R5" t="n">
-        <v>7181670</v>
+        <v>7181685</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1126,7 +1126,7 @@
         <v>130190569</v>
       </c>
       <c r="B6" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24496-2025 artfynd.xlsx
+++ b/artfynd/A 24496-2025 artfynd.xlsx
@@ -899,27 +899,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130190556</v>
+        <v>130190570</v>
       </c>
       <c r="B4" t="n">
-        <v>57865</v>
+        <v>58224</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>761916</v>
+        <v>761900</v>
       </c>
       <c r="R4" t="n">
-        <v>7181670</v>
+        <v>7181685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1011,27 +1011,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130190570</v>
+        <v>130190556</v>
       </c>
       <c r="B5" t="n">
-        <v>58224</v>
+        <v>57865</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>761900</v>
+        <v>761916</v>
       </c>
       <c r="R5" t="n">
-        <v>7181685</v>
+        <v>7181670</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 24496-2025 artfynd.xlsx
+++ b/artfynd/A 24496-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130190573</v>
       </c>
       <c r="B2" t="n">
-        <v>83053</v>
+        <v>83054</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130190567</v>
       </c>
       <c r="B3" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,27 +899,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130190570</v>
+        <v>130190556</v>
       </c>
       <c r="B4" t="n">
-        <v>58224</v>
+        <v>57865</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>761900</v>
+        <v>761916</v>
       </c>
       <c r="R4" t="n">
-        <v>7181685</v>
+        <v>7181670</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1011,27 +1011,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130190556</v>
+        <v>130190570</v>
       </c>
       <c r="B5" t="n">
-        <v>57865</v>
+        <v>58224</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>761916</v>
+        <v>761900</v>
       </c>
       <c r="R5" t="n">
-        <v>7181670</v>
+        <v>7181685</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 24496-2025 artfynd.xlsx
+++ b/artfynd/A 24496-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130190573</v>
       </c>
       <c r="B2" t="n">
-        <v>83054</v>
+        <v>83055</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130190567</v>
       </c>
       <c r="B3" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,27 +899,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130190556</v>
+        <v>130190570</v>
       </c>
       <c r="B4" t="n">
-        <v>57865</v>
+        <v>58224</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>761916</v>
+        <v>761900</v>
       </c>
       <c r="R4" t="n">
-        <v>7181670</v>
+        <v>7181685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1011,27 +1011,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130190570</v>
+        <v>130190556</v>
       </c>
       <c r="B5" t="n">
-        <v>58224</v>
+        <v>57865</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>761900</v>
+        <v>761916</v>
       </c>
       <c r="R5" t="n">
-        <v>7181685</v>
+        <v>7181670</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 24496-2025 artfynd.xlsx
+++ b/artfynd/A 24496-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130190573</v>
       </c>
       <c r="B2" t="n">
-        <v>83055</v>
+        <v>83057</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130190567</v>
       </c>
       <c r="B3" t="n">
-        <v>91723</v>
+        <v>91725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,27 +899,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130190570</v>
+        <v>130190556</v>
       </c>
       <c r="B4" t="n">
-        <v>58224</v>
+        <v>57867</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>761900</v>
+        <v>761916</v>
       </c>
       <c r="R4" t="n">
-        <v>7181685</v>
+        <v>7181670</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1011,27 +1011,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130190556</v>
+        <v>130190570</v>
       </c>
       <c r="B5" t="n">
-        <v>57865</v>
+        <v>58226</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>761916</v>
+        <v>761900</v>
       </c>
       <c r="R5" t="n">
-        <v>7181670</v>
+        <v>7181685</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1126,7 +1126,7 @@
         <v>130190569</v>
       </c>
       <c r="B6" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24496-2025 artfynd.xlsx
+++ b/artfynd/A 24496-2025 artfynd.xlsx
@@ -899,27 +899,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130190556</v>
+        <v>130190570</v>
       </c>
       <c r="B4" t="n">
-        <v>57867</v>
+        <v>58226</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>761916</v>
+        <v>761900</v>
       </c>
       <c r="R4" t="n">
-        <v>7181670</v>
+        <v>7181685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1011,27 +1011,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130190570</v>
+        <v>130190556</v>
       </c>
       <c r="B5" t="n">
-        <v>58226</v>
+        <v>57867</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>761900</v>
+        <v>761916</v>
       </c>
       <c r="R5" t="n">
-        <v>7181685</v>
+        <v>7181670</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 24496-2025 artfynd.xlsx
+++ b/artfynd/A 24496-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>130190573</v>
       </c>
       <c r="B2" t="n">
-        <v>83057</v>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130190567</v>
       </c>
       <c r="B3" t="n">
-        <v>91725</v>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,27 +899,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130190570</v>
+        <v>130190556</v>
       </c>
       <c r="B4" t="n">
-        <v>58226</v>
+        <v>57966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>761900</v>
+        <v>761916</v>
       </c>
       <c r="R4" t="n">
-        <v>7181685</v>
+        <v>7181670</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1011,27 +1011,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130190556</v>
+        <v>130190570</v>
       </c>
       <c r="B5" t="n">
-        <v>57867</v>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>761916</v>
+        <v>761900</v>
       </c>
       <c r="R5" t="n">
-        <v>7181670</v>
+        <v>7181685</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1126,7 +1126,7 @@
         <v>130190569</v>
       </c>
       <c r="B6" t="n">
-        <v>58013</v>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>130190565</v>
       </c>
       <c r="B7" t="n">
-        <v>8440</v>
+        <v>8444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,6 +1344,118 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130190574</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skellefteå-Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>761910</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7181691</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>NVI (C250260) Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Elin Lönnberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24496-2025 artfynd.xlsx
+++ b/artfynd/A 24496-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130190573</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130190567</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130190556</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130190570</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130190569</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130190565</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1456,8 +1491,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130190574</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>